--- a/datasets/05_elc_employee_performance/originals/mock_data.xlsx
+++ b/datasets/05_elc_employee_performance/originals/mock_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongn\Downloads\files (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{E087C1D9-F9C3-4130-9F7E-3A667C205985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F4DE69-CCEB-4F43-AF53-B4ADDC32153D}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E087C1D9-F9C3-4130-9F7E-3A667C205985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3BD957-76A6-4B70-9ACF-9DCAF69C7BFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 LEGEND &amp; SUMMARY" sheetId="1" r:id="rId1"/>
@@ -3443,17 +3443,17 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -3756,6 +3756,33 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B67E3A47-E76D-4AD8-834D-208A979409BD}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;5f507b9c-3925-4aea-991f-568ea9d17322&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F113"/>
@@ -3770,7 +3797,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="16"/>
@@ -3788,7 +3815,7 @@
       <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="16"/>
@@ -3814,7 +3841,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -3936,7 +3963,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -4088,7 +4115,7 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -4195,7 +4222,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -4422,7 +4449,7 @@
       </c>
     </row>
     <row r="53" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="13" t="s">
         <v>118</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -4589,7 +4616,7 @@
       </c>
     </row>
     <row r="65" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="13" t="s">
         <v>150</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -4666,7 +4693,7 @@
       </c>
     </row>
     <row r="71" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="13" t="s">
         <v>160</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -4788,7 +4815,7 @@
       </c>
     </row>
     <row r="80" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>178</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -4850,7 +4877,7 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="13" t="s">
         <v>187</v>
       </c>
       <c r="C85" s="8" t="s">
@@ -4897,7 +4924,7 @@
       </c>
     </row>
     <row r="89" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="13" t="s">
         <v>194</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -5019,7 +5046,7 @@
       </c>
     </row>
     <row r="98" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>217</v>
       </c>
       <c r="C98" s="8" t="s">
@@ -5186,7 +5213,7 @@
       </c>
     </row>
     <row r="110" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="13" t="s">
         <v>240</v>
       </c>
       <c r="C110" s="11" t="s">
@@ -5249,6 +5276,10 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B9:B16"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B98:B108"/>
     <mergeCell ref="B80:B83"/>
@@ -5260,10 +5291,6 @@
     <mergeCell ref="B65:B69"/>
     <mergeCell ref="B37:B51"/>
     <mergeCell ref="B89:B96"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="B18:B27"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B9:B16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
